--- a/expert-system/output/statistics/statistics.xlsx
+++ b/expert-system/output/statistics/statistics.xlsx
@@ -17,6 +17,8 @@
     <sheet name="TS-STAT-Access" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="TS-STAT-DataCache" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="TS-STAT-Export" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="TS-STAT-EffBounds" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="TS-STAT-CacheArch" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Feature Matrix'!$A$1:$G$9</definedName>
@@ -28,6 +30,8 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'TS-STAT-Access'!$A$3:$J$12</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'TS-STAT-DataCache'!$A$3:$J$12</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'TS-STAT-Export'!$A$3:$J$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'TS-STAT-EffBounds'!$A$3:$J$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'TS-STAT-CacheArch'!$A$3:$J$15</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -171,7 +175,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -204,6 +208,18 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -572,7 +588,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B45"/>
+  <dimension ref="A1:E47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -586,6 +602,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -642,7 +659,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>138</t>
         </is>
       </c>
     </row>
@@ -654,7 +671,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
     </row>
@@ -682,6 +699,7 @@
         </is>
       </c>
     </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
@@ -738,6 +756,7 @@
         </is>
       </c>
     </row>
+    <row r="20"/>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
@@ -794,106 +813,126 @@
         </is>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>Effective Bounds on Individual Norm — 15 cases</t>
+        </is>
+      </c>
+    </row>
     <row r="30">
-      <c r="A30" s="4" t="inlineStr">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>Caching Architecture &amp; Performance (#3337) — 12 cases</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
         <is>
           <t>Knowledge Sources</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  - modules/statistics-service-implementation.md — backend (6 design issues, norm calc, 3 update paths)</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  - modules/frontend-statistics-module.md — frontend (12 tech debt items, dual sub-systems)</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - exploration/ui-flows/statistics-ui-deep-exploration.md — live UI testing across roles (S29)</t>
+          <t xml:space="preserve">  - modules/statistics-service-implementation.md — backend (6 design issues, norm calc, 3 update paths)</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - exploration/api-findings/statistics-api-testing.md — 10 endpoints tested, mixed units found</t>
+          <t xml:space="preserve">  - modules/frontend-statistics-module.md — frontend (12 tech debt items, dual sub-systems)</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - exploration/api-findings/statistics-cross-env-comparison.md — TM vs Stage field differences</t>
+          <t xml:space="preserve">  - exploration/ui-flows/statistics-ui-deep-exploration.md — live UI testing across roles (S29)</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
         <is>
+          <t xml:space="preserve">  - exploration/api-findings/statistics-api-testing.md — 10 endpoints tested, mixed units found</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - exploration/api-findings/statistics-cross-env-comparison.md — TM vs Stage field differences</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="6" t="inlineStr">
+        <is>
           <t xml:space="preserve">  - external/tickets/ticket-3400-statistics-individual-norm-export.md — not in codebase</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="4" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="4" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
         <is>
           <t>Test Data Generation</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  - Employee logins: Use known test accounts — alsmirnov (EMPLOYEE-only), pvaynmaster (multi-role 7+), perekrest (multi-role)</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  - Date ranges: Current month for live data, previous month for closed period data</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - Norm scenarios: Find employees via DB: SELECT * FROM statistic_report WHERE month_norm != budget_norm (admin vacation cases)</t>
+          <t xml:space="preserve">  - Employee logins: Use known test accounts — alsmirnov (EMPLOYEE-only), pvaynmaster (multi-role 7+), perekrest (multi-role)</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - Over/under report: Filter by excess &gt; 10 or excess &lt; -10 in statistic_report table</t>
+          <t xml:space="preserve">  - Date ranges: Current month for live data, previous month for closed period data</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - Absence data: Cross-reference vacation/sick_leave tables with statistic_report for same employee/month</t>
+          <t xml:space="preserve">  - Norm scenarios: Find employees via DB: SELECT * FROM statistic_report WHERE month_norm != budget_norm (admin vacation cases)</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - API auth: Use API_SECRET_TOKEN from env config for full-access API testing</t>
+          <t xml:space="preserve">  - Over/under report: Filter by excess &gt; 10 or excess &lt; -10 in statistic_report table</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - Absence data: Cross-reference vacation/sick_leave tables with statistic_report for same employee/month</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - API auth: Use API_SECRET_TOKEN from env config for full-access API testing</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">  - Cross-env: Test same employee on both timemachine and stage for field comparison tests</t>
         </is>
@@ -908,6 +947,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A26" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A27" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A28" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A29" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A30" r:id="rId9"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1446,6 +1487,2210 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="002F5496"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="55" customWidth="1" min="4" max="4"/>
+    <col width="45" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="25" customWidth="1" min="9" max="9"/>
+    <col width="35" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="16" t="inlineStr">
+        <is>
+          <t>&lt;- Back to Plan</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Suite: Effective Bounds on Individual Norm (#3353, #3356, #3381)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="17" t="inlineStr">
+        <is>
+          <t>Test ID</t>
+        </is>
+      </c>
+      <c r="B3" s="17" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="C3" s="17" t="inlineStr">
+        <is>
+          <t>Preconditions</t>
+        </is>
+      </c>
+      <c r="D3" s="17" t="inlineStr">
+        <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>Expected Result</t>
+        </is>
+      </c>
+      <c r="F3" s="17" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="G3" s="17" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="H3" s="17" t="inlineStr">
+        <is>
+          <t>Requirement Ref</t>
+        </is>
+      </c>
+      <c r="I3" s="17" t="inlineStr">
+        <is>
+          <t>Module/Component</t>
+        </is>
+      </c>
+      <c r="J3" s="17" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>TC-STAT-112</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>Effective bounds — employee hired mid-month (prorated personalNorm)</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>Employee hired mid-month (e.g., Feb 15).
+Find test data:
+  SELECT e.login, e.full_name, ewp.first_working_day, ewp.last_working_day
+  FROM employee e
+  JOIN employee_work_period ewp ON e.id = ewp.employee_id
+  WHERE EXTRACT(DAY FROM ewp.first_working_day) &gt; 1
+    AND EXTRACT(DAY FROM ewp.first_working_day) &lt;= 20
+    AND e.enabled = true
+  ORDER BY ewp.first_working_day DESC LIMIT 5;
+Identify the month containing the hire date.
+Verify employee_work_period record exists for this employee.</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>1. GET /api/ttt/v1/statistic/report?employeeId={id}&amp;year={Y}&amp;month={M}
+   where M = hire month.
+2. Check response field personalNorm (or month_norm in DB).
+3. Calculate expected: count working days from hire date to end of month
+   using production calendar, multiply by 8.
+   E.g., Feb 15-28 in Russian calendar = 10 working days x 8h = 80h.
+4. DB: SELECT month_norm, budget_norm FROM statistic_report
+   WHERE employee_id = {id} AND year = {Y} AND month = {M}.
+5. Navigate to Statistics &gt; Employee Reports for the employee.
+6. Verify UI displays the prorated norm, not full month norm.</t>
+        </is>
+      </c>
+      <c r="E4" s="8" t="inlineStr">
+        <is>
+          <t>personalNorm is prorated to actual working days within effective bounds.
+For Feb 15-28 hire: ~80h (not full 160h).
+statistic_report.month_norm matches the prorated value.
+UI Employee Reports table shows the clamped norm.
+My Tasks counter uses the effective-bounded norm for percentage calculation.</t>
+        </is>
+      </c>
+      <c r="F4" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="H4" s="8" t="inlineStr">
+        <is>
+          <t>#3353, #3356</t>
+        </is>
+      </c>
+      <c r="I4" s="8" t="inlineStr">
+        <is>
+          <t>Statistics / Norm Calculation</t>
+        </is>
+      </c>
+      <c r="J4" s="8" t="inlineStr">
+        <is>
+          <t>Core feature: effectiveFrom = max(monthStart, firstWorkingDay). Verify NormForDateCalculator.getEffectiveBounds() applies correctly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>TC-STAT-113</t>
+        </is>
+      </c>
+      <c r="B5" s="10" t="inlineStr">
+        <is>
+          <t>Effective bounds — employee dismissed mid-month (norm capped at dismissal)</t>
+        </is>
+      </c>
+      <c r="C5" s="10" t="inlineStr">
+        <is>
+          <t>Employee dismissed mid-month.
+Find test data:
+  SELECT e.login, e.full_name, ewp.first_working_day, ewp.last_working_day
+  FROM employee e
+  JOIN employee_work_period ewp ON e.id = ewp.employee_id
+  WHERE ewp.last_working_day IS NOT NULL
+    AND EXTRACT(DAY FROM ewp.last_working_day) &lt; 28
+    AND EXTRACT(DAY FROM ewp.last_working_day) &gt; 1
+    AND e.enabled = true
+  ORDER BY ewp.last_working_day DESC LIMIT 5;
+Identify the month containing the dismissal date.</t>
+        </is>
+      </c>
+      <c r="D5" s="10" t="inlineStr">
+        <is>
+          <t>1. GET /api/ttt/v1/statistic/report?employeeId={id}&amp;year={Y}&amp;month={M}
+   where M = dismissal month.
+2. Check personalNorm value.
+3. Calculate expected: count working days from month start to dismissal date
+   using production calendar, multiply by 8.
+4. DB: SELECT month_norm FROM statistic_report
+   WHERE employee_id = {id} AND year = {Y} AND month = {M}.
+5. Compare month_norm with full-month norm for that office.
+6. Verify month_norm &lt; full-month norm.</t>
+        </is>
+      </c>
+      <c r="E5" s="10" t="inlineStr">
+        <is>
+          <t>personalNorm covers only working days up to dismissal date.
+statistic_report.month_norm reflects the truncated range.
+E.g., if dismissed Feb 14: norm = working days Feb 1-14 x 8h.
+Norm is strictly less than full month norm for the office.
+effectiveTo = min(monthEnd, lastWorkingDay) applied correctly.</t>
+        </is>
+      </c>
+      <c r="F5" s="10" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G5" s="10" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="H5" s="10" t="inlineStr">
+        <is>
+          <t>#3353, #3356</t>
+        </is>
+      </c>
+      <c r="I5" s="10" t="inlineStr">
+        <is>
+          <t>Statistics / Norm Calculation</t>
+        </is>
+      </c>
+      <c r="J5" s="10" t="inlineStr">
+        <is>
+          <t>effectiveTo = min(monthEnd, lastWorkingDay). Verify last_working_day from employee_work_period is used, not employee.dismissal_date directly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>TC-STAT-114</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>Effective bounds — employee not yet employed for target month (norm = 0)</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>Employee hired in a future month relative to the queried month.
+Find test data:
+  SELECT e.login, ewp.first_working_day
+  FROM employee e
+  JOIN employee_work_period ewp ON e.id = ewp.employee_id
+  WHERE ewp.first_working_day &gt; CURRENT_DATE
+    AND e.enabled = true
+  LIMIT 5;
+If none found, use an employee hired this month and query the previous month.</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>1. GET /api/ttt/v1/statistic/report?employeeId={id}&amp;year={Y}&amp;month={M}
+   where the month is BEFORE the employee's first_working_day.
+2. Check personalNorm value.
+3. DB: SELECT month_norm FROM statistic_report
+   WHERE employee_id = {id} AND year = {Y} AND month = {M}.
+4. Verify norm is 0 or that no record exists for that month.
+5. Check that the API does not return an error (graceful handling).</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>personalNorm = 0 for months before employee's first working day.
+API returns norm=0 (not an error or null).
+No statistic_report record may exist, OR record exists with month_norm=0.
+Effective bounds: effectiveFrom &gt; monthEnd means no overlap, norm=0.</t>
+        </is>
+      </c>
+      <c r="F6" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="H6" s="8" t="inlineStr">
+        <is>
+          <t>#3353, #3356</t>
+        </is>
+      </c>
+      <c r="I6" s="8" t="inlineStr">
+        <is>
+          <t>Statistics / Norm Calculation</t>
+        </is>
+      </c>
+      <c r="J6" s="8" t="inlineStr">
+        <is>
+          <t>Edge case: when effectiveFrom &gt; monthEnd, the date range is empty. Verify no division-by-zero or NPE in norm calculation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>TC-STAT-115</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>Effective bounds — re-hired employee with gap in employment</t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="inlineStr">
+        <is>
+          <t>Employee with multiple work periods (gap in employment).
+Find test data:
+  SELECT e.login, e.full_name, COUNT(*) AS period_count
+  FROM employee e
+  JOIN employee_work_period ewp ON e.id = ewp.employee_id
+  WHERE e.enabled = true
+  GROUP BY e.id
+  HAVING COUNT(*) &gt; 1
+  LIMIT 5;
+Then: SELECT * FROM employee_work_period
+WHERE employee_id = {id} ORDER BY first_working_day;
+Identify the gap month(s) and the re-hire month.</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="inlineStr">
+        <is>
+          <t>1. For the re-hire month, GET /api/ttt/v1/statistic/report for the employee.
+2. Check which work period is used for norm calculation.
+3. For a month in the gap (between periods), query the same endpoint.
+4. DB: SELECT month_norm FROM statistic_report for gap month.
+5. For the re-hire month, verify norm is prorated from the new first_working_day.
+6. Verify gap months have norm = 0.</t>
+        </is>
+      </c>
+      <c r="E7" s="10" t="inlineStr">
+        <is>
+          <t>Re-hire month: personalNorm prorated from new first_working_day to month end.
+Gap months: personalNorm = 0 (no active work period).
+Most recent matching work period used for current calculations.
+Old work period does not bleed into gap months.</t>
+        </is>
+      </c>
+      <c r="F7" s="10" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G7" s="10" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="H7" s="10" t="inlineStr">
+        <is>
+          <t>#3353, #3356</t>
+        </is>
+      </c>
+      <c r="I7" s="10" t="inlineStr">
+        <is>
+          <t>Statistics / Norm Calculation</t>
+        </is>
+      </c>
+      <c r="J7" s="10" t="inlineStr">
+        <is>
+          <t>Multiple employee_work_period records. The system should match the work period that overlaps with the target month. Verify no period confusion when multiple records exist.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>TC-STAT-116</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>Effective bounds — no work period data (fallback to full month)</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>Employee with no records in employee_work_period table.
+Find test data:
+  SELECT e.login, e.full_name
+  FROM employee e
+  LEFT JOIN employee_work_period ewp ON e.id = ewp.employee_id
+  WHERE e.enabled = true AND ewp.id IS NULL
+  LIMIT 5;
+These employees may exist if work period sync has not run or data is missing.</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>1. GET /api/ttt/v1/statistic/report?employeeId={id}&amp;year={Y}&amp;month={M}.
+2. Check personalNorm value.
+3. Compare with the full month norm for the employee's office.
+4. DB: SELECT month_norm FROM statistic_report for the employee/month.
+5. Verify the system does not crash or return an error.
+6. Check application logs for warnings about missing work period.</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>System uses full month range as fallback when no work period data exists.
+personalNorm = full month norm for the employee's office/calendar.
+No crash, NPE, or 500 error.
+Behavior matches pre-#3353 behavior (backward compatible).
+Optional: warning logged about missing work period.</t>
+        </is>
+      </c>
+      <c r="F8" s="8" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>Error Handling</t>
+        </is>
+      </c>
+      <c r="H8" s="8" t="inlineStr">
+        <is>
+          <t>#3353</t>
+        </is>
+      </c>
+      <c r="I8" s="8" t="inlineStr">
+        <is>
+          <t>Statistics / Norm Calculation</t>
+        </is>
+      </c>
+      <c r="J8" s="8" t="inlineStr">
+        <is>
+          <t>Fallback behavior: if employee_work_period is empty, effectiveFrom = monthStart and effectiveTo = monthEnd. Verify graceful degradation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>TC-STAT-117</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>Budget norm — employee with admin vacation (budgetNorm &gt; personalNorm)</t>
+        </is>
+      </c>
+      <c r="C9" s="10" t="inlineStr">
+        <is>
+          <t>Employee who had administrative vacation (leave type = ADMIN) during the target month.
+Find test data:
+  SELECT sr.employee_id, e.login, sr.month_norm, sr.budget_norm,
+         sr.year, sr.month
+  FROM statistic_report sr
+  JOIN employee e ON sr.employee_id = e.id
+  WHERE sr.budget_norm &gt; sr.month_norm
+    AND sr.budget_norm &gt; 0
+  ORDER BY sr.year DESC, sr.month DESC
+  LIMIT 5;
+Also verify admin vacation exists:
+  SELECT * FROM vacation
+  WHERE employee_id = {id}
+    AND type = 'ADMINISTRATIVE'
+    AND EXTRACT(YEAR FROM start_date) = {Y}
+    AND EXTRACT(MONTH FROM start_date) = {M};</t>
+        </is>
+      </c>
+      <c r="D9" s="10" t="inlineStr">
+        <is>
+          <t>1. GET /api/ttt/v1/statistic/report?employeeId={id}&amp;year={Y}&amp;month={M}.
+2. Check both personalNorm and budgetNorm fields in response.
+3. Verify budgetNorm = personalNorm + (admin_vacation_hours).
+4. Navigate to Statistics &gt; Employee Reports for the employee/month.
+5. Check UI display format: should show '{personalNorm} ({budgetNorm})'.
+6. Verify the excess percentage uses budgetNorm as denominator.</t>
+        </is>
+      </c>
+      <c r="E9" s="10" t="inlineStr">
+        <is>
+          <t>budgetNorm &gt; personalNorm (includes admin vacation hours).
+UI shows dual display: e.g., '144 (160)' where 144 = personalNorm, 160 = budgetNorm.
+Budget norm = personalNorm + admin_vacation_working_days * 8.
+Excess calculation: (reported - budgetNorm) / budgetNorm * 100.</t>
+        </is>
+      </c>
+      <c r="F9" s="10" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G9" s="10" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="H9" s="10" t="inlineStr">
+        <is>
+          <t>#3381</t>
+        </is>
+      </c>
+      <c r="I9" s="10" t="inlineStr">
+        <is>
+          <t>Statistics / Norm Calculation</t>
+        </is>
+      </c>
+      <c r="J9" s="10" t="inlineStr">
+        <is>
+          <t>budgetNorm is a new field added by #3381. Verify it appears in both API response and UI. The dual display format is specific to employee reports.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>TC-STAT-118</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>Budget norm — no admin vacation (budgetNorm equals personalNorm)</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>Employee with no administrative vacation in the target month.
+Find test data:
+  SELECT sr.employee_id, e.login, sr.month_norm, sr.budget_norm,
+         sr.year, sr.month
+  FROM statistic_report sr
+  JOIN employee e ON sr.employee_id = e.id
+  WHERE sr.budget_norm = sr.month_norm
+    AND sr.month_norm &gt; 0
+    AND e.enabled = true
+  ORDER BY sr.year DESC, sr.month DESC
+  LIMIT 5;</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>1. GET /api/ttt/v1/statistic/report?employeeId={id}&amp;year={Y}&amp;month={M}.
+2. Check personalNorm and budgetNorm fields.
+3. Verify budgetNorm = personalNorm.
+4. Navigate to Statistics &gt; Employee Reports for the employee.
+5. Check UI display: should show single number (no parenthetical).
+6. DB: Confirm no ADMINISTRATIVE vacation for that employee/month.</t>
+        </is>
+      </c>
+      <c r="E10" s="8" t="inlineStr">
+        <is>
+          <t>budgetNorm equals personalNorm when no admin vacation exists.
+UI shows single norm value (no dual display, no parentheses).
+E.g., just '160' not '160 (160)'.
+Excess calculation: (reported - personalNorm) / personalNorm * 100.</t>
+        </is>
+      </c>
+      <c r="F10" s="8" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="H10" s="8" t="inlineStr">
+        <is>
+          <t>#3381</t>
+        </is>
+      </c>
+      <c r="I10" s="8" t="inlineStr">
+        <is>
+          <t>Statistics / Norm Calculation</t>
+        </is>
+      </c>
+      <c r="J10" s="8" t="inlineStr">
+        <is>
+          <t>When budgetNorm = personalNorm, UI should not show redundant parenthetical. Verify frontend conditionally renders the dual format.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>TC-STAT-119</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>Budget norm + effective bounds — partial-month employee with admin vacation</t>
+        </is>
+      </c>
+      <c r="C11" s="10" t="inlineStr">
+        <is>
+          <t>Employee hired mid-month who also has admin vacation in that same month.
+Find test data:
+  SELECT sr.employee_id, e.login, sr.month_norm, sr.budget_norm,
+         ewp.first_working_day
+  FROM statistic_report sr
+  JOIN employee e ON sr.employee_id = e.id
+  JOIN employee_work_period ewp ON e.id = ewp.employee_id
+  WHERE sr.budget_norm &gt; sr.month_norm
+    AND sr.month_norm &lt; 160
+    AND EXTRACT(DAY FROM ewp.first_working_day) &gt; 1
+  ORDER BY sr.year DESC, sr.month DESC
+  LIMIT 5;
+If none found, this is a manufactured scenario: use timemachine clock to create it.</t>
+        </is>
+      </c>
+      <c r="D11" s="10" t="inlineStr">
+        <is>
+          <t>1. DB: Get employee's first_working_day and admin vacation dates for the month.
+2. Calculate expected personalNorm: working days within [firstWorkingDay, monthEnd] * 8.
+3. Calculate expected budgetNorm: personalNorm + admin_vacation_hours_within_bounds.
+4. GET /api/ttt/v1/statistic/report for the employee/month.
+5. Compare API personalNorm with expected.
+6. Compare API budgetNorm with expected.
+7. Verify admin vacation hours are clamped to within effective bounds
+   (not the full month).</t>
+        </is>
+      </c>
+      <c r="E11" s="10" t="inlineStr">
+        <is>
+          <t>Both effective bounds AND admin vacation exclusion apply correctly.
+personalNorm: prorated to actual work period (&lt; full month).
+budgetNorm: personalNorm + admin vacation hours WITHIN the effective bounds.
+Admin vacation days outside the effective bounds are NOT counted.
+E.g., hired Feb 15, admin vacation Feb 10-12 (before hire) should not add to budget.</t>
+        </is>
+      </c>
+      <c r="F11" s="10" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G11" s="10" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="H11" s="10" t="inlineStr">
+        <is>
+          <t>#3353, #3381</t>
+        </is>
+      </c>
+      <c r="I11" s="10" t="inlineStr">
+        <is>
+          <t>Statistics / Norm Calculation</t>
+        </is>
+      </c>
+      <c r="J11" s="10" t="inlineStr">
+        <is>
+          <t>Interaction test: effective bounds clamping intersected with admin vacation period. The admin vacation hours should only count for days within the employee's effective work period, not the full calendar month.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>TC-STAT-120</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>Excess calculation uses budgetNorm as denominator</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>Employee with budgetNorm &gt; personalNorm (has admin vacation).
+Employee has reported hours for the month.
+Reuse employee from TC-STAT-117.
+  SELECT sr.employee_id, e.login, sr.month_norm, sr.budget_norm,
+         sr.month_hours, sr.excess
+  FROM statistic_report sr
+  JOIN employee e ON sr.employee_id = e.id
+  WHERE sr.budget_norm &gt; sr.month_norm
+    AND sr.month_hours &gt; 0
+  ORDER BY sr.year DESC, sr.month DESC
+  LIMIT 5;</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>1. DB: Get month_hours, month_norm, budget_norm, excess for the employee.
+2. Calculate: expected_excess = (month_hours - budget_norm) / budget_norm * 100.
+3. Compare with stored excess value.
+4. Also calculate incorrect version: (month_hours - month_norm) / month_norm * 100.
+5. Verify stored excess matches budgetNorm-based calculation, not personalNorm-based.
+6. Navigate to Statistics &gt; Employee Reports and check displayed excess percentage.</t>
+        </is>
+      </c>
+      <c r="E12" s="8" t="inlineStr">
+        <is>
+          <t>excess = (reported - budgetNorm) / budgetNorm * 100.
+NOT: (reported - personalNorm) / personalNorm * 100.
+The denominator is budgetNorm, which includes admin vacation hours.
+This means employees with admin vacation show lower excess percentages.
+UI excess display matches the DB value.</t>
+        </is>
+      </c>
+      <c r="F12" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="H12" s="8" t="inlineStr">
+        <is>
+          <t>#3381</t>
+        </is>
+      </c>
+      <c r="I12" s="8" t="inlineStr">
+        <is>
+          <t>Statistics / Norm Calculation</t>
+        </is>
+      </c>
+      <c r="J12" s="8" t="inlineStr">
+        <is>
+          <t>Critical: if excess still uses personalNorm as denominator, admin vacation employees will show artificially high excess. Verify the formula change.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>TC-STAT-121</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>normForDate — current month progressive accumulation within effective bounds</t>
+        </is>
+      </c>
+      <c r="C13" s="10" t="inlineStr">
+        <is>
+          <t>Employee currently active (not dismissed, hired before current month).
+Current date is mid-month (e.g., March 15).
+Employee hired before this month (full effective bounds for current month).</t>
+        </is>
+      </c>
+      <c r="D13" s="10" t="inlineStr">
+        <is>
+          <t>1. GET /api/ttt/v1/statistic/report?employeeId={id}&amp;year={Y}&amp;month={M}
+   where M = current month.
+2. Note the personalNorm (full month) and normForDate (progressive).
+3. Calculate expected normForDate: working days from month start to today * 8.
+4. Verify normForDate &lt;= personalNorm.
+5. Check the next day: normForDate should increase by 8 (if working day)
+   or stay the same (if weekend/holiday).
+6. Verify normForDate is clamped within effective bounds:
+   max(monthStart, firstWorkingDay) to min(today, lastWorkingDay).</t>
+        </is>
+      </c>
+      <c r="E13" s="10" t="inlineStr">
+        <is>
+          <t>normForDate accumulates day by day within effective bounds.
+On March 15: normForDate = working days [monthStart..March 15] * 8.
+normForDate &lt;= personalNorm always.
+normForDate increases on working days, stays flat on weekends/holidays.
+Effective bounds applied: normForDate never exceeds what the clamped range allows.</t>
+        </is>
+      </c>
+      <c r="F13" s="10" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G13" s="10" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="H13" s="10" t="inlineStr">
+        <is>
+          <t>#3353, #3356</t>
+        </is>
+      </c>
+      <c r="I13" s="10" t="inlineStr">
+        <is>
+          <t>Statistics / Norm Calculation</t>
+        </is>
+      </c>
+      <c r="J13" s="10" t="inlineStr">
+        <is>
+          <t>normForDate = progressive norm up to current date. Used for 'current status' indicators. Verify it respects effective bounds, not just calendar month.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>TC-STAT-122</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>normForDate — employee hired after the selected date (norm = 0)</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>Employee hired mid-month (e.g., Feb 15).
+Query normForDate for a date BEFORE the hire date (e.g., Feb 10).
+Reuse employee from TC-STAT-112.</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>1. GET /api/ttt/v1/statistic/report?employeeId={id}&amp;year={Y}&amp;month={M}&amp;date={D}
+   where D = a date before the employee's first_working_day within the same month.
+   (If API does not accept date param, check via DB or timemachine clock.)
+2. DB: SELECT * FROM statistic_report WHERE employee_id = {id}
+   AND year = {Y} AND month = {M}.
+3. Calculate expected normForDate: effective range = [firstWorkingDay, date].
+   Since date &lt; firstWorkingDay, effective range is empty.
+4. Verify normForDate = 0.
+5. Check that personalNorm (full month value) is still correctly prorated.</t>
+        </is>
+      </c>
+      <c r="E14" s="8" t="inlineStr">
+        <is>
+          <t>normForDate = 0 when the selected date is before the employee's first working day.
+Effective range is empty: max(monthStart, firstWorkingDay) &gt; min(date, monthEnd).
+personalNorm is still correctly prorated for the full month.
+No error or negative value returned.</t>
+        </is>
+      </c>
+      <c r="F14" s="8" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G14" s="8" t="inlineStr">
+        <is>
+          <t>Boundary</t>
+        </is>
+      </c>
+      <c r="H14" s="8" t="inlineStr">
+        <is>
+          <t>#3353, #3356</t>
+        </is>
+      </c>
+      <c r="I14" s="8" t="inlineStr">
+        <is>
+          <t>Statistics / Norm Calculation</t>
+        </is>
+      </c>
+      <c r="J14" s="8" t="inlineStr">
+        <is>
+          <t>Tests the case where the normForDate range collapses to empty. The progressive norm should be 0, not negative or full-month.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>TC-STAT-123</t>
+        </is>
+      </c>
+      <c r="B15" s="10" t="inlineStr">
+        <is>
+          <t>normForDate — employee dismissed before the selected date (norm capped at dismissal)</t>
+        </is>
+      </c>
+      <c r="C15" s="10" t="inlineStr">
+        <is>
+          <t>Employee dismissed mid-month (e.g., Feb 10).
+Query normForDate for a date AFTER the dismissal (e.g., Feb 15).
+Reuse employee from TC-STAT-113.</t>
+        </is>
+      </c>
+      <c r="D15" s="10" t="inlineStr">
+        <is>
+          <t>1. GET /api/ttt/v1/statistic/report?employeeId={id}&amp;year={Y}&amp;month={M}
+   for the dismissal month, using a date after dismissal.
+2. DB: SELECT month_norm FROM statistic_report
+   WHERE employee_id = {id} AND year = {Y} AND month = {M}.
+3. Calculate expected normForDate:
+   effective range = [monthStart, min(date, lastWorkingDay)].
+   Since date &gt; lastWorkingDay, clamped to [monthStart, lastWorkingDay].
+4. Verify normForDate = personalNorm (fully accumulated up to dismissal).
+5. Verify normForDate does NOT continue growing after dismissal date.</t>
+        </is>
+      </c>
+      <c r="E15" s="10" t="inlineStr">
+        <is>
+          <t>normForDate is capped at the dismissal date.
+normForDate = personalNorm once the selected date passes lastWorkingDay.
+No additional hours accumulate after dismissal.
+E.g., Feb 10 dismissal: normForDate on Feb 15 = same as normForDate on Feb 10.
+effectiveTo = min(date, lastWorkingDay) correctly applied.</t>
+        </is>
+      </c>
+      <c r="F15" s="10" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G15" s="10" t="inlineStr">
+        <is>
+          <t>Boundary</t>
+        </is>
+      </c>
+      <c r="H15" s="10" t="inlineStr">
+        <is>
+          <t>#3353, #3356</t>
+        </is>
+      </c>
+      <c r="I15" s="10" t="inlineStr">
+        <is>
+          <t>Statistics / Norm Calculation</t>
+        </is>
+      </c>
+      <c r="J15" s="10" t="inlineStr">
+        <is>
+          <t>After dismissal, normForDate should plateau at personalNorm. Verify the progressive calculation stops at lastWorkingDay.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>TC-STAT-124</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>Sync path — norm updated via vacation event (create/modify vacation)</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>Employee with existing statistic_report for current month.
+No admin vacation yet for this month.
+Find test data:
+  SELECT sr.employee_id, e.login, sr.month_norm, sr.budget_norm
+  FROM statistic_report sr
+  JOIN employee e ON sr.employee_id = e.id
+  WHERE sr.month_norm = sr.budget_norm
+    AND sr.year = EXTRACT(YEAR FROM CURRENT_DATE)
+    AND sr.month = EXTRACT(MONTH FROM CURRENT_DATE)
+    AND e.enabled = true
+  LIMIT 5;</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t>1. DB: Record current month_norm and budget_norm for the employee.
+2. Create an admin vacation for this employee in the current month:
+   POST /api/vacation/v1/vacation/create (type=ADMINISTRATIVE, 2 working days).
+3. Wait for event propagation (MQ message: VACATION_CREATED).
+4. DB: Re-query statistic_report for the employee/month.
+5. Verify budget_norm increased by 16 (2 days * 8h).
+6. Verify month_norm unchanged (effective bounds not affected by vacation).
+7. Check that effective bounds are still correctly applied to month_norm.</t>
+        </is>
+      </c>
+      <c r="E16" s="8" t="inlineStr">
+        <is>
+          <t>After vacation creation:
+  - budget_norm = previous_budget_norm + 16 (2 admin days * 8h).
+  - month_norm unchanged (effective bounds clamping unaffected).
+  - Event-driven update path correctly recalculates budget_norm.
+  - Effective bounds still applied to month_norm in the recalculation.
+If effective bounds are NOT applied during event-driven recalc,
+month_norm may revert to full-month value (regression).</t>
+        </is>
+      </c>
+      <c r="F16" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G16" s="8" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="H16" s="8" t="inlineStr">
+        <is>
+          <t>#3353, #3381</t>
+        </is>
+      </c>
+      <c r="I16" s="8" t="inlineStr">
+        <is>
+          <t>Statistics / Sync</t>
+        </is>
+      </c>
+      <c r="J16" s="8" t="inlineStr">
+        <is>
+          <t>Tests the MQ event-driven update path (StatisticReportService.onVacationEvent). Effective bounds must be applied during event-triggered recalculation, not just during cron sync. Requires allow_api_mutations=true or manual action.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="10" t="inlineStr">
+        <is>
+          <t>TC-STAT-125</t>
+        </is>
+      </c>
+      <c r="B17" s="10" t="inlineStr">
+        <is>
+          <t>Sync path — norm updated via task report submission</t>
+        </is>
+      </c>
+      <c r="C17" s="10" t="inlineStr">
+        <is>
+          <t>Employee with existing statistic_report for current month.
+Employee has fewer reported hours than norm.
+  SELECT sr.employee_id, e.login, sr.month_norm, sr.month_hours
+  FROM statistic_report sr
+  JOIN employee e ON sr.employee_id = e.id
+  WHERE sr.month_hours &lt; sr.month_norm
+    AND sr.year = EXTRACT(YEAR FROM CURRENT_DATE)
+    AND sr.month = EXTRACT(MONTH FROM CURRENT_DATE)
+    AND e.enabled = true
+  LIMIT 5;</t>
+        </is>
+      </c>
+      <c r="D17" s="10" t="inlineStr">
+        <is>
+          <t>1. DB: Record current month_norm, budget_norm, month_hours for the employee.
+2. Submit a time report for the employee (8h on a working day):
+   POST /api/ttt/v1/report (or via UI).
+3. Wait for statistic_report update (event-driven or poll DB).
+4. DB: Re-query statistic_report.
+5. Verify month_hours increased by 8.
+6. Verify month_norm still reflects effective bounds (not recalculated to full month).
+7. Verify excess recalculated with updated hours but same norm values.</t>
+        </is>
+      </c>
+      <c r="E17" s="10" t="inlineStr">
+        <is>
+          <t>After task report submission:
+  - month_hours increased by 8.
+  - month_norm unchanged (effective bounds still applied).
+  - budget_norm unchanged.
+  - excess recalculated: (new_month_hours - budget_norm) / budget_norm * 100.
+If month_norm reverts to full-month during report-triggered recalc,
+this is a regression in effective bounds.</t>
+        </is>
+      </c>
+      <c r="F17" s="10" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G17" s="10" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="H17" s="10" t="inlineStr">
+        <is>
+          <t>#3353</t>
+        </is>
+      </c>
+      <c r="I17" s="10" t="inlineStr">
+        <is>
+          <t>Statistics / Sync</t>
+        </is>
+      </c>
+      <c r="J17" s="10" t="inlineStr">
+        <is>
+          <t>Tests the task-report-driven update path. The critical check is that month_norm is NOT recalculated to full-month value during this path. Requires allow_api_mutations=true or manual action.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="8" t="inlineStr">
+        <is>
+          <t>TC-STAT-126</t>
+        </is>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>Sync path — norm updated via daily cron sync (04:00 job)</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>Employees with statistic_report records.
+At least one employee hired mid-month (for effective bounds verification).
+At least one employee with admin vacation (for budget norm verification).
+  -- Mid-month hire:
+  SELECT sr.employee_id, e.login, sr.month_norm
+  FROM statistic_report sr
+  JOIN employee e ON sr.employee_id = e.id
+  JOIN employee_work_period ewp ON e.id = ewp.employee_id
+  WHERE EXTRACT(DAY FROM ewp.first_working_day) &gt; 1
+    AND sr.year = EXTRACT(YEAR FROM CURRENT_DATE)
+    AND sr.month = EXTRACT(MONTH FROM CURRENT_DATE)
+  LIMIT 3;
+  -- Admin vacation:
+  SELECT sr.employee_id, e.login, sr.budget_norm
+  FROM statistic_report sr
+  JOIN employee e ON sr.employee_id = e.id
+  WHERE sr.budget_norm &gt; sr.month_norm
+    AND sr.year = EXTRACT(YEAR FROM CURRENT_DATE)
+    AND sr.month = EXTRACT(MONTH FROM CURRENT_DATE)
+  LIMIT 3;</t>
+        </is>
+      </c>
+      <c r="D18" s="8" t="inlineStr">
+        <is>
+          <t>1. DB: Record month_norm and budget_norm for selected employees.
+2. Trigger the nightly sync manually:
+   POST /v1/test/trigger-optimized-statistic-report-sync
+   (or wait for the 04:00 cron job).
+3. DB: Re-query statistic_report for the same employees.
+4. For mid-month hire: verify month_norm is still prorated (not full month).
+5. For admin vacation: verify budget_norm still includes admin vacation hours.
+6. Verify both previous month and current month records are correct.
+7. Check that the sync did not reset effective bounds.</t>
+        </is>
+      </c>
+      <c r="E18" s="8" t="inlineStr">
+        <is>
+          <t>After daily cron sync:
+  - Mid-month hires: month_norm remains prorated (effective bounds preserved).
+  - Admin vacation employees: budget_norm remains &gt; month_norm.
+  - Previous month records: fully finalized with correct effective bounds.
+  - Current month records: progressive normForDate correctly bounded.
+Cron sync applies the same effective bounds logic as event-driven updates.
+No regression: norms not reset to full-month values.</t>
+        </is>
+      </c>
+      <c r="F18" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G18" s="8" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="H18" s="8" t="inlineStr">
+        <is>
+          <t>#3353, #3356, #3381</t>
+        </is>
+      </c>
+      <c r="I18" s="8" t="inlineStr">
+        <is>
+          <t>Statistics / Sync</t>
+        </is>
+      </c>
+      <c r="J18" s="8" t="inlineStr">
+        <is>
+          <t>Tests the nightly cron sync path (OptimizedStatisticReportSyncJob). All three norm components (personalNorm, budgetNorm, normForDate) must respect effective bounds after sync. This is the most common recalculation trigger.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A3:J18"/>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A1" r:id="rId1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="002F5496"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="55" customWidth="1" min="4" max="4"/>
+    <col width="45" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="25" customWidth="1" min="9" max="9"/>
+    <col width="35" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="16" t="inlineStr">
+        <is>
+          <t>&lt;- Back to Plan</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Suite: Caching Architecture &amp; Performance (#3337)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="17" t="inlineStr">
+        <is>
+          <t>Test ID</t>
+        </is>
+      </c>
+      <c r="B3" s="17" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="C3" s="17" t="inlineStr">
+        <is>
+          <t>Preconditions</t>
+        </is>
+      </c>
+      <c r="D3" s="17" t="inlineStr">
+        <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>Expected Result</t>
+        </is>
+      </c>
+      <c r="F3" s="17" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="G3" s="17" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="H3" s="17" t="inlineStr">
+        <is>
+          <t>Requirement Ref</t>
+        </is>
+      </c>
+      <c r="I3" s="17" t="inlineStr">
+        <is>
+          <t>Module/Component</t>
+        </is>
+      </c>
+      <c r="J3" s="17" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>TC-STAT-127</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>POST /v1/statistic bulk request returns vacation statistics for multiple employees</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>Multiple employees with reported hours in the target month.
+Find test data:
+  SELECT DISTINCT sr.employee_login
+  FROM statistic_report sr
+  WHERE sr.year = EXTRACT(YEAR FROM CURRENT_DATE)
+    AND sr.month = EXTRACT(MONTH FROM CURRENT_DATE) - 1
+  LIMIT 20;
+Collect 5-10 employee logins for the request body.
+Use timemachine or qa-1 env.</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>1. POST /api/ttt/v1/statistic
+   Body: {"employeesLogins": ["login1","login2",...],
+          "startDate": "YYYY-MM-01", "endDate": "YYYY-MM-28"}
+2. Verify response contains statistics for each requested employee.
+3. Verify response includes fields: login, personalNorm, budgetNorm,
+   reportedEffort (or reported), excess.
+4. Verify OLD endpoint no longer works:
+   GET /api/ttt/v1/statistic?employeeLogin=X&amp;startDate=...&amp;endDate=...
+   Should return 405 Method Not Allowed (or similar).
+5. DB: Cross-verify with statistic_report table:
+   SELECT employee_login, month_norm, reported_effort
+   FROM statistic_report
+   WHERE employee_login IN ('login1','login2',...)
+     AND report_date = 'YYYY-MM-01';
+6. Verify response data matches DB cached values.</t>
+        </is>
+      </c>
+      <c r="E4" s="8" t="inlineStr">
+        <is>
+          <t>POST /v1/statistic returns bulk statistics for all requested employees.
+Response data matches pre-computed values in statistic_report table.
+No cross-service calls at query time (fast response).
+Old GET endpoint returns 405 or 404 (endpoint changed to POST).
+Response contains: personalNorm, budgetNorm, reported, excess per employee.
+reported_effort field type is BigDecimal (not double).</t>
+        </is>
+      </c>
+      <c r="F4" s="8" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="H4" s="8" t="inlineStr">
+        <is>
+          <t>#3337</t>
+        </is>
+      </c>
+      <c r="I4" s="8" t="inlineStr">
+        <is>
+          <t>Statistics / API / StatisticController</t>
+        </is>
+      </c>
+      <c r="J4" s="8" t="inlineStr">
+        <is>
+          <t>MR !5150 changed GET→POST. MR !5013 changed backend to read from statistic_report table. Verify both: endpoint method AND data source.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>TC-STAT-128</t>
+        </is>
+      </c>
+      <c r="B5" s="10" t="inlineStr">
+        <is>
+          <t>POST /v1/statistic/sick-leaves bulk request returns sick leave stats</t>
+        </is>
+      </c>
+      <c r="C5" s="10" t="inlineStr">
+        <is>
+          <t>Multiple employees with sick leaves in the target period.
+Find test data:
+  SELECT DISTINCT sl.employee_login
+  FROM sick_leave sl
+  WHERE sl.start_date &gt;= 'YYYY-01-01'
+  LIMIT 10;
+Collect 5-10 logins with sick leaves.</t>
+        </is>
+      </c>
+      <c r="D5" s="10" t="inlineStr">
+        <is>
+          <t>1. POST /api/ttt/v1/statistic/sick-leaves
+   Body: {"employeesLogins": ["login1","login2",...],
+          "startDate": "YYYY-01-01", "endDate": "YYYY-12-31"}
+2. Verify response contains sick leave data per employee.
+3. Verify OLD endpoint no longer works:
+   GET /api/ttt/v1/statistic/sick-leaves?...
+   Should return 405.
+4. Test with empty logins array: {"employeesLogins": []}
+   Expect empty response, not error.
+5. Test with single login: {"employeesLogins": ["login1"]}
+   Verify equivalent to per-employee query.
+6. Verify sickLeaves field is an object (not string) in response.</t>
+        </is>
+      </c>
+      <c r="E5" s="10" t="inlineStr">
+        <is>
+          <t>POST /v1/statistic/sick-leaves returns bulk sick leave data.
+Empty logins array → empty response (not error).
+Single login → correct per-employee data.
+Old GET endpoint returns 405.
+sickLeaves field type is object (MR !5155 fixed PropTypes).
+Response time significantly faster than old batched GET approach.</t>
+        </is>
+      </c>
+      <c r="F5" s="10" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G5" s="10" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="H5" s="10" t="inlineStr">
+        <is>
+          <t>#3337</t>
+        </is>
+      </c>
+      <c r="I5" s="10" t="inlineStr">
+        <is>
+          <t>Statistics / API / StatisticReportController</t>
+        </is>
+      </c>
+      <c r="J5" s="10" t="inlineStr">
+        <is>
+          <t>MR !5150 changed sick-leaves endpoint from GET to POST. MR !5155 fixed frontend PropTypes (string→object). Verify both.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>TC-STAT-129</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>Statistics: Admin/Chief Accountant sees ALL employees in report</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>User with ADMIN or CHIEF_ACCOUNTANT role.
+Find admin user:
+  SELECT e.login FROM employee e
+  JOIN employee_role er ON e.id = er.employee_id
+  WHERE er.role = 'ROLE_ADMIN'
+    AND e.enabled = true
+  LIMIT 3;</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>1. Login as ADMIN user.
+2. Navigate to Statistics &gt; Employee Reports.
+3. Select a reporting period (e.g., previous month).
+4. Count total employees shown in the table.
+5. DB: Count all enabled employees:
+   SELECT COUNT(*) FROM employee WHERE enabled = true;
+6. Verify the table shows ALL employees (not filtered).
+7. POST /api/ttt/v1/statistic with all employee logins.
+8. Verify all logins are returned in response.
+9. Repeat for CHIEF_ACCOUNTANT role — same result expected.</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>ADMIN and CHIEF_ACCOUNTANT see all employees in statistics.
+No filtering applied: employee count matches total enabled employees.
+API returns data for every requested login.
+Both roles have identical visibility scope.</t>
+        </is>
+      </c>
+      <c r="F6" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="H6" s="8" t="inlineStr">
+        <is>
+          <t>#3337</t>
+        </is>
+      </c>
+      <c r="I6" s="8" t="inlineStr">
+        <is>
+          <t>Statistics / Access Control / Role Filtering</t>
+        </is>
+      </c>
+      <c r="J6" s="8" t="inlineStr">
+        <is>
+          <t>MR !5101 added getEmployeeLoginsByCurrentUserRole() which returns null for ADMIN and CHIEF_ACCOUNTANT (null = no filter = see all).</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>TC-STAT-130</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>Statistics: Department Manager sees only direct reports</t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="inlineStr">
+        <is>
+          <t>User with DEPARTMENT_MANAGER role who manages a team.
+Find DM user:
+  SELECT e.login, e.full_name FROM employee e
+  JOIN employee_role er ON e.id = er.employee_id
+  WHERE er.role = 'ROLE_DEPARTMENT_MANAGER'
+    AND e.enabled = true
+  LIMIT 3;
+Find their direct reports:
+  SELECT e.login FROM employee e
+  WHERE e.manager_id = {dm_id}
+    AND e.enabled = true;</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="inlineStr">
+        <is>
+          <t>1. Login as DEPARTMENT_MANAGER user.
+2. Navigate to Statistics &gt; Employee Reports.
+3. Select a reporting period.
+4. Note the employees shown in the table.
+5. DB: Get DM's direct reports:
+   SELECT e.login FROM employee e
+   WHERE e.manager_id = (SELECT id FROM employee WHERE login = '{dm_login}')
+   AND e.enabled = true;
+6. Verify the table shows ONLY the DM's direct reports.
+7. Verify the DM cannot see employees from other departments.
+8. API: POST /v1/statistic with a login NOT in DM's reports.
+   Verify that employee is excluded from response.</t>
+        </is>
+      </c>
+      <c r="E7" s="10" t="inlineStr">
+        <is>
+          <t>Department Manager sees ONLY their direct reports.
+Employee count matches DB query for manager_id = DM's ID.
+Employees from other departments NOT visible.
+API filters out non-managed employees from response.
+DM cannot access other managers' team statistics.</t>
+        </is>
+      </c>
+      <c r="F7" s="10" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G7" s="10" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="H7" s="10" t="inlineStr">
+        <is>
+          <t>#3337</t>
+        </is>
+      </c>
+      <c r="I7" s="10" t="inlineStr">
+        <is>
+          <t>Statistics / Access Control / Role Filtering</t>
+        </is>
+      </c>
+      <c r="J7" s="10" t="inlineStr">
+        <is>
+          <t>MR !5101: ROLE_DEPARTMENT_MANAGER → filter by managerId. Uses EmployeeRepository.findAllByOfficesOrManagers() JPQL query.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>TC-STAT-131</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>Statistics: Tech Lead sees only their assigned employees</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>User with TECH_LEAD role.
+Find TL user:
+  SELECT e.login FROM employee e
+  JOIN employee_role er ON e.id = er.employee_id
+  WHERE er.role = 'ROLE_TECH_LEAD'
+    AND e.enabled = true
+  LIMIT 3;
+Find their employees:
+  SELECT e.login FROM employee e
+  WHERE e.tech_lead_id = {tl_id}
+    AND e.enabled = true;</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>1. Login as TECH_LEAD user.
+2. Navigate to Statistics &gt; Employee Reports.
+3. Select a reporting period.
+4. Note the employees shown.
+5. DB: Get TL's employees:
+   SELECT e.login FROM employee e
+   WHERE e.tech_lead_id = (SELECT id FROM employee WHERE login = '{tl_login}')
+   AND e.enabled = true;
+6. Verify the table shows ONLY the TL's employees.
+7. Compare with OFFICE_DIRECTOR/ACCOUNTANT visibility:
+   - Login as OFFICE_DIRECTOR → sees employees in their profit centers.
+   - Login as ACCOUNTANT → sees employees in their profit centers.
+8. Verify each role sees its expected scope.</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>Tech Lead sees ONLY employees where tech_lead_id matches.
+Office Director sees employees in their profit center offices.
+Accountant sees employees in their profit center offices.
+Each role's filter is applied independently.
+Scopes may overlap (same employee visible to multiple roles).</t>
+        </is>
+      </c>
+      <c r="F8" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="H8" s="8" t="inlineStr">
+        <is>
+          <t>#3337</t>
+        </is>
+      </c>
+      <c r="I8" s="8" t="inlineStr">
+        <is>
+          <t>Statistics / Access Control / Role Filtering</t>
+        </is>
+      </c>
+      <c r="J8" s="8" t="inlineStr">
+        <is>
+          <t>MR !5101: ROLE_TECH_LEAD → filter by techLeadId. ROLE_OFFICE_DIRECTOR/ROLE_ACCOUNTANT → filter by officeIds. ROLE_OFFICE_HR → filter by hrId. Tests multiple role scopes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>TC-STAT-132</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>Cache: Vacation create/delete updates month_norm via RabbitMQ event</t>
+        </is>
+      </c>
+      <c r="C9" s="10" t="inlineStr">
+        <is>
+          <t>Employee with statistic_report record for current month.
+No administrative vacation in current month.
+  SELECT sr.employee_login, sr.month_norm, sr.budget_norm
+  FROM statistic_report sr
+  WHERE sr.month_norm = sr.budget_norm
+    AND sr.year = EXTRACT(YEAR FROM CURRENT_DATE)
+    AND sr.month = EXTRACT(MONTH FROM CURRENT_DATE)
+  LIMIT 5;
+Use timemachine env with allow_api_mutations=true.</t>
+        </is>
+      </c>
+      <c r="D9" s="10" t="inlineStr">
+        <is>
+          <t>1. DB: Record current month_norm, budget_norm for employee.
+2. Create an administrative vacation for this month:
+   POST /api/vacation/v1/vacation/create
+   (type=ADMINISTRATIVE, 3 working days in current month).
+3. Wait 5-10 seconds for RabbitMQ event propagation.
+4. DB: Re-query statistic_report:
+   SELECT month_norm, budget_norm, reported_effort
+   FROM statistic_report
+   WHERE employee_login = '{login}'
+     AND year = {Y} AND month = {M};
+5. Verify budget_norm increased by 24 (3 days × 8h).
+6. Verify month_norm unchanged.
+7. Delete the vacation.
+8. Wait for event propagation.
+9. Re-query: verify budget_norm reverted to original value.
+10. Navigate to Statistics page — verify UI reflects changes.</t>
+        </is>
+      </c>
+      <c r="E9" s="10" t="inlineStr">
+        <is>
+          <t>After vacation creation:
+  - budget_norm = original + 24 (3 admin days × 8h).
+  - month_norm unchanged (not affected by admin vacation).
+  - reported_effort unchanged.
+After vacation deletion:
+  - budget_norm reverts to original value.
+  - Event-driven: update happens within seconds (not waiting for 4am cron).
+MQ path: Vacation service publishes EmployeeMonthNormContextCalculated
+event → RabbitMQ → TTT service consumes and updates statistic_report.</t>
+        </is>
+      </c>
+      <c r="F9" s="10" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="G9" s="10" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="H9" s="10" t="inlineStr">
+        <is>
+          <t>#3337</t>
+        </is>
+      </c>
+      <c r="I9" s="10" t="inlineStr">
+        <is>
+          <t>Statistics / Cache / RabbitMQ</t>
+        </is>
+      </c>
+      <c r="J9" s="10" t="inlineStr">
+        <is>
+          <t>MR !5013: RabbitMQ topic exchange TTT_BACKEND_EMPLOYEE_TOPIC. Vacation service publishes event, TTT service consumes. This tests the complete cross-service event-driven update path.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>TC-STAT-133</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>Cache: Sick leave create/change/delete updates month_norm</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>Employee with statistic_report record for current month.
+No existing sick leave in current month.
+  SELECT sr.employee_login, sr.month_norm
+  FROM statistic_report sr
+  WHERE sr.year = EXTRACT(YEAR FROM CURRENT_DATE)
+    AND sr.month = EXTRACT(MONTH FROM CURRENT_DATE)
+  LIMIT 5;
+Use timemachine env with allow_api_mutations=true.</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>1. DB: Record current month_norm for employee.
+2. Create a sick leave for the employee in current month (5 days):
+   POST /api/vacation/v1/sick-leave/create
+3. Wait 5-10 seconds for event propagation.
+4. DB: Re-query statistic_report month_norm.
+5. Verify month_norm decreased (sick leave reduces working days).
+6. Change the sick leave (extend to 7 days):
+   PATCH /api/vacation/v1/sick-leave/{id}
+7. Wait, re-query. Verify month_norm decreased further.
+8. Delete the sick leave.
+9. Wait, re-query. Verify month_norm reverted to original.
+10. For sick leave spanning two months (e.g., Jan 28 - Feb 3):
+    Verify BOTH months' statistic_report records updated.</t>
+        </is>
+      </c>
+      <c r="E10" s="8" t="inlineStr">
+        <is>
+          <t>Sick leave creation reduces month_norm (fewer working days).
+Sick leave change (extend/shorten) updates month_norm accordingly.
+Sick leave deletion restores original month_norm.
+Cross-month sick leave: events published for EACH affected month.
+Updates happen event-driven (within seconds), not waiting for cron.
+BUG (pre-fix, MR !5200): month_norm did NOT update on sick leave —
+only updated by daily cron. Verify this is now fixed.</t>
+        </is>
+      </c>
+      <c r="F10" s="8" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="H10" s="8" t="inlineStr">
+        <is>
+          <t>#3337</t>
+        </is>
+      </c>
+      <c r="I10" s="8" t="inlineStr">
+        <is>
+          <t>Statistics / Cache / Sick Leave Events</t>
+        </is>
+      </c>
+      <c r="J10" s="8" t="inlineStr">
+        <is>
+          <t>MR !5200 added sick leave event handlers: SickLeaveCreated/Changed/DeletedEventListener → sendUpdateMonthNormEvent(sickLeave). Multi-month sick leaves publish separate events per month. QA Bug #2 from omaksimova — verify fix.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>TC-STAT-134</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>Cache: Task report add/patch/delete updates reported_effort</t>
+        </is>
+      </c>
+      <c r="C11" s="10" t="inlineStr">
+        <is>
+          <t>Employee with statistic_report record for current month.
+Employee has reported some hours this month.
+  SELECT sr.employee_login, sr.reported_effort, sr.month_norm
+  FROM statistic_report sr
+  WHERE sr.reported_effort &gt; 0
+    AND sr.year = EXTRACT(YEAR FROM CURRENT_DATE)
+    AND sr.month = EXTRACT(MONTH FROM CURRENT_DATE)
+  LIMIT 5;
+Use timemachine env with allow_api_mutations=true.</t>
+        </is>
+      </c>
+      <c r="D11" s="10" t="inlineStr">
+        <is>
+          <t>1. DB: Record current reported_effort for employee.
+2. Add a task report (8h) for the employee in current month:
+   POST /api/ttt/v1/report (effort: 8, date in current month).
+3. DB: Re-query reported_effort immediately.
+4. Verify reported_effort increased by 8.000.
+5. Patch the report to 4h:
+   PATCH /api/ttt/v1/report/{id} (effort: 4).
+6. Verify reported_effort decreased by 4.000.
+7. Delete the report:
+   DELETE /api/ttt/v1/report/{id}.
+8. Verify reported_effort decreased by 4.000.
+9. Verify month_norm was NOT changed by task report events.
+10. Navigate to Statistics page — verify UI shows updated reported.</t>
+        </is>
+      </c>
+      <c r="E11" s="10" t="inlineStr">
+        <is>
+          <t>Task report add: reported_effort increases by effort amount.
+Task report patch: reported_effort adjusts to new effort.
+Task report delete: reported_effort decreases accordingly.
+reported_effort type is DECIMAL(10,3) — values like 8.000.
+month_norm NOT affected by task report events.
+Update is synchronous via TaskReportEventListener (not MQ).
+Excess recalculated: (reported_effort - budget_norm) / budget_norm × 100.</t>
+        </is>
+      </c>
+      <c r="F11" s="10" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G11" s="10" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="H11" s="10" t="inlineStr">
+        <is>
+          <t>#3337</t>
+        </is>
+      </c>
+      <c r="I11" s="10" t="inlineStr">
+        <is>
+          <t>Statistics / Cache / Task Report Events</t>
+        </is>
+      </c>
+      <c r="J11" s="10" t="inlineStr">
+        <is>
+          <t>MR !5013: TaskReportEventListener calls statisticReportSyncService.updateMonthlyReportedEffortForEmployee() on add/patch/delete. This is direct service call, not MQ. Verify update is immediate, not deferred.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>TC-STAT-135</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>Cache: Event type discrimination — absence events do NOT delete unrelated records</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>Multiple employees with statistic_report records.
+Employee A has vacation. Employee B has NO vacation but has statistic_report.
+Find test data:
+  -- Employee A (with vacation):
+  SELECT DISTINCT sr.employee_login
+  FROM statistic_report sr
+  JOIN vacation v ON sr.employee_login = (
+    SELECT login FROM employee WHERE id = v.employee_id)
+  WHERE sr.year = EXTRACT(YEAR FROM CURRENT_DATE)
+  LIMIT 3;
+  -- Employee B (no vacation, has stat report):
+  SELECT sr.employee_login FROM statistic_report sr
+  WHERE sr.year = EXTRACT(YEAR FROM CURRENT_DATE)
+    AND sr.employee_login NOT IN (
+      SELECT e.login FROM employee e
+      JOIN vacation v ON e.id = v.employee_id
+      WHERE v.status NOT IN ('DELETED','CANCELED'))
+  LIMIT 3;</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>1. DB: Record statistic_report records for Employee B.
+   SELECT * FROM statistic_report
+   WHERE employee_login = '{B_login}';
+2. Create a vacation for Employee A (not B).
+3. Wait for event propagation (5-10 sec).
+4. DB: Re-query statistic_report for Employee B.
+   Verify ALL records still exist (not deleted).
+5. Verify Employee A's records were correctly updated.
+6. DB: Count total statistic_report records before and after.
+   SELECT COUNT(*) FROM statistic_report;
+7. Verify total count did not decrease (no unrelated deletions).
+8. Repeat with sick leave event — same verification.</t>
+        </is>
+      </c>
+      <c r="E12" s="8" t="inlineStr">
+        <is>
+          <t>Vacation/sick leave events for Employee A do NOT delete
+Employee B's statistic_report records.
+Only INITIAL_SYNC event type triggers deleteReportsWithEmploymentChanged().
+VACATION_CHANGES and SICK_LEAVE_CHANGES event types skip deletion.
+Total statistic_report record count stable after absence events.
+BUG (pre-fix, MR !5203): absence events triggered deletion of
+unrelated employees' records via deleteReportsWithEmploymentChanged().
+This was the most critical bug in the caching implementation.</t>
+        </is>
+      </c>
+      <c r="F12" s="8" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="H12" s="8" t="inlineStr">
+        <is>
+          <t>#3337</t>
+        </is>
+      </c>
+      <c r="I12" s="8" t="inlineStr">
+        <is>
+          <t>Statistics / Cache / Event Type Discrimination</t>
+        </is>
+      </c>
+      <c r="J12" s="8" t="inlineStr">
+        <is>
+          <t>MR !5203: New enum StatisticReportUpdateEventType with INITIAL_SYNC, VACATION_CHANGES, SICK_LEAVE_CHANGES. deleteReportsWithEmploymentChanged() only on INITIAL_SYNC. QA Bug #3 / dev comment by Quyen Nguyen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>TC-STAT-136</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>Frontend: Empty/null statistics response clears loading state</t>
+        </is>
+      </c>
+      <c r="C13" s="10" t="inlineStr">
+        <is>
+          <t>Employee with NO statistic_report records for a specific month.
+Find months with no data:
+  SELECT DISTINCT year, month FROM statistic_report
+  ORDER BY year, month;
+  -- Pick a month NOT in this list, or use a month far in the future.</t>
+        </is>
+      </c>
+      <c r="D13" s="10" t="inlineStr">
+        <is>
+          <t>1. Navigate to Statistics &gt; Employee Reports.
+2. Select a reporting period with data — verify table loads normally.
+3. Switch to a period with NO data (e.g., far future month).
+4. Verify:
+   a. Loading spinner appears briefly.
+   b. Loading spinner disappears (not infinite).
+   c. Table shows empty state (no rows, or 'No data' message).
+   d. No stale data from previous period displayed.
+5. Switch back to a period with data — verify table loads correctly.
+6. Rapidly switch between periods (stress test saga cancellation).
+7. Verify no JavaScript console errors.</t>
+        </is>
+      </c>
+      <c r="E13" s="10" t="inlineStr">
+        <is>
+          <t>Empty/null response: loading state cleared, table shows empty.
+No infinite loading spinner.
+No stale data from previous period retained.
+Period switching: previous request cancelled, new data loaded.
+No console errors or uncaught promise rejections.
+BUG (pre-fix, MR !5194): empty response left isLoadingReports=true
+(infinite spinner) and stale reports[] data displayed.</t>
+        </is>
+      </c>
+      <c r="F13" s="10" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G13" s="10" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="H13" s="10" t="inlineStr">
+        <is>
+          <t>#3337</t>
+        </is>
+      </c>
+      <c r="I13" s="10" t="inlineStr">
+        <is>
+          <t>Statistics / Frontend / Redux Reducer</t>
+        </is>
+      </c>
+      <c r="J13" s="10" t="inlineStr">
+        <is>
+          <t>MR !5194: On empty/null response, dispatches fetchReportsFailureAction(). Reducer now clears state.reports = [] on failure. QA Bug #1 from omaksimova (infinite loading on out-of-employment period).</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>TC-STAT-137</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>Frontend: Rapid period switching cancels pending requests (saga cancellation)</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>Logged-in user with access to Statistics &gt; Employee Reports.
+Multiple reporting periods with data available.</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>1. Navigate to Statistics &gt; Employee Reports.
+2. Select period Jan 2026 — wait for table to start loading.
+3. IMMEDIATELY switch to Feb 2026 (before Jan data arrives).
+4. IMMEDIATELY switch to Mar 2026 (before Feb data arrives).
+5. Wait for final request to complete.
+6. Verify:
+   a. Table shows March 2026 data (the last requested period).
+   b. No mixing of Jan/Feb/Mar data in the table.
+   c. No duplicate rows from multiple responses.
+   d. Loading indicator properly reflects final state.
+7. Open browser DevTools &gt; Network tab.
+8. Repeat the rapid switching.
+9. Verify cancelled requests show as 'cancelled' in Network tab.
+10. Check browser console for errors.</t>
+        </is>
+      </c>
+      <c r="E14" s="8" t="inlineStr">
+        <is>
+          <t>Final table shows ONLY the last requested period data.
+Previous requests are cancelled (visible in Network tab).
+No data mixing between periods.
+No duplicate rows or partial data.
+Redux saga uses task.isRunning() check before starting new fetch.
+Map&lt;string, Task&gt; properly tracks and cancels previous tasks.
+No unhandled promise rejections from cancelled requests.</t>
+        </is>
+      </c>
+      <c r="F14" s="8" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G14" s="8" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="H14" s="8" t="inlineStr">
+        <is>
+          <t>#3337</t>
+        </is>
+      </c>
+      <c r="I14" s="8" t="inlineStr">
+        <is>
+          <t>Statistics / Frontend / Saga Cancellation</t>
+        </is>
+      </c>
+      <c r="J14" s="8" t="inlineStr">
+        <is>
+          <t>MR !5155: Rewrote sagas with task.isRunning() and Map&lt;string, Task&gt; for improved cancellation. Previous implementation used raw objects and was prone to race conditions on rapid period switching.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>TC-STAT-138</t>
+        </is>
+      </c>
+      <c r="B15" s="10" t="inlineStr">
+        <is>
+          <t>Daily cron sync (4am) correctly populates statistic_report for current + previous month</t>
+        </is>
+      </c>
+      <c r="C15" s="10" t="inlineStr">
+        <is>
+          <t>statistic_report table exists with some records.
+At least one employee has reported hours in current month.
+At least one employee has a vacation in previous month.
+Use timemachine env (can trigger sync manually).</t>
+        </is>
+      </c>
+      <c r="D15" s="10" t="inlineStr">
+        <is>
+          <t>1. DB: Record current statistic_report state:
+   SELECT employee_login, year, month, reported_effort, month_norm,
+          budget_norm
+   FROM statistic_report
+   WHERE (year = EXTRACT(YEAR FROM CURRENT_DATE)
+     AND month = EXTRACT(MONTH FROM CURRENT_DATE))
+   OR (year = EXTRACT(YEAR FROM CURRENT_DATE)
+     AND month = EXTRACT(MONTH FROM CURRENT_DATE) - 1)
+   ORDER BY employee_login, year, month;
+2. Trigger sync via test endpoint:
+   POST /api/ttt/v1/test/trigger-optimized-statistic-report-sync
+   (or POST /api/ttt/v1/test/statistic-reports for direct sync).
+3. Wait for sync to complete (may take 30-60 seconds).
+4. Re-query statistic_report for current + previous month.
+5. Verify:
+   a. All active employees have records for both months.
+   b. reported_effort matches actual task reports:
+      SELECT employee_id, SUM(effort) FROM task_report
+      WHERE EXTRACT(YEAR FROM report_date) = {Y}
+        AND EXTRACT(MONTH FROM report_date) = {M}
+      GROUP BY employee_id;
+   c. month_norm reflects effective bounds (prorated for partial months).
+   d. budget_norm includes admin vacation hours.
+6. Check ShedLock table for scheduled job state:
+   SELECT * FROM shedlock WHERE name LIKE '%statistic%';</t>
+        </is>
+      </c>
+      <c r="E15" s="10" t="inlineStr">
+        <is>
+          <t>Cron sync populates statistic_report for current AND previous month.
+All active employees have records for both months.
+reported_effort matches SUM(task_report.effort) for the month.
+month_norm reflects effective bounds (not full calendar month).
+budget_norm includes admin vacation hours where applicable.
+ShedLock prevents concurrent execution.
+Cron schedule: 0 0 4 * * ? (daily at 4:00 AM).
+StatisticReportSyncLauncher syncs previous + current month.
+Uses StatisticReportSyncService.saveMonthNormAndReportedEffortForEmployees()
+with eventType=INITIAL_SYNC (triggers deleteReportsWithEmploymentChanged).</t>
+        </is>
+      </c>
+      <c r="F15" s="10" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G15" s="10" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="H15" s="10" t="inlineStr">
+        <is>
+          <t>#3337</t>
+        </is>
+      </c>
+      <c r="I15" s="10" t="inlineStr">
+        <is>
+          <t>Statistics / Sync / Cron Job</t>
+        </is>
+      </c>
+      <c r="J15" s="10" t="inlineStr">
+        <is>
+          <t>MR !5013: StatisticReportScheduler at 0 0 4 * * ? with ShedLock. StatisticReportSyncLauncher runs for previous and current month. Uses INITIAL_SYNC event type which DOES trigger employment change deletion. Test endpoint: POST /v1/test/statistic-reports.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A3:J15"/>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A1" r:id="rId1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -1453,7 +3698,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1692,25 +3937,79 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="12" t="inlineStr">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>Effective Bounds</t>
+        </is>
+      </c>
+      <c r="B9" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="18" t="n">
+        <v>15</v>
+      </c>
+      <c r="D9" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="18" t="n">
+        <v>15</v>
+      </c>
+      <c r="G9" s="19" t="inlineStr">
+        <is>
+          <t>TS-STAT-EffBounds</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>Caching Architecture</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="C10" s="20" t="n">
+        <v>6</v>
+      </c>
+      <c r="D10" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="F10" s="20" t="n">
+        <v>12</v>
+      </c>
+      <c r="G10" s="21" t="inlineStr">
+        <is>
+          <t>TS-STAT-CacheArch</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="12" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B9" s="12" t="n">
+      <c r="B11" s="12" t="n">
         <v>59</v>
       </c>
-      <c r="C9" s="12" t="n">
-        <v>24</v>
-      </c>
-      <c r="D9" s="12" t="n">
+      <c r="C11" s="12" t="n">
+        <v>39</v>
+      </c>
+      <c r="D11" s="12" t="n">
         <v>19</v>
       </c>
-      <c r="E9" s="12" t="n">
+      <c r="E11" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="F9" s="12" t="n">
-        <v>111</v>
+      <c r="F11" s="12" t="n">
+        <v>138</v>
       </c>
     </row>
   </sheetData>
@@ -1723,6 +4022,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G10" r:id="rId9"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
